--- a/設定ファイル/シリアル_48us/シリアル_48us_CLK3.xlsx
+++ b/設定ファイル/シリアル_48us/シリアル_48us_CLK3.xlsx
@@ -1,44 +1,223 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e12206\GitHub\DCDC_clock_simulator\設定ファイル\シリアル_48us\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53D95349-7C1C-42F3-9EF2-90739BECF3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="4150" yWindow="0" windowWidth="14550" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="config" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="config" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+  <si>
+    <t>parameter</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>pl_dcdc_clk_name</t>
+  </si>
+  <si>
+    <t>PL_DCDC_CLK3</t>
+  </si>
+  <si>
+    <t>pl_dcdc_clk_delay_clks</t>
+  </si>
+  <si>
+    <t>pl_dcdc_clk_delay_ns</t>
+  </si>
+  <si>
+    <t>power_net_name_0</t>
+  </si>
+  <si>
+    <t>4.3V_CHG</t>
+  </si>
+  <si>
+    <t>power_net_name_1</t>
+  </si>
+  <si>
+    <t>power_net_name_2</t>
+  </si>
+  <si>
+    <t>power_net_name_3</t>
+  </si>
+  <si>
+    <t>power_net_name_4</t>
+  </si>
+  <si>
+    <t>power_net_name_5</t>
+  </si>
+  <si>
+    <t>power_net_name_6</t>
+  </si>
+  <si>
+    <t>power_net_name_7</t>
+  </si>
+  <si>
+    <t>power_net_delay_ns_0</t>
+  </si>
+  <si>
+    <t>power_net_delay_ns_1</t>
+  </si>
+  <si>
+    <t>power_net_delay_ns_2</t>
+  </si>
+  <si>
+    <t>power_net_delay_ns_3</t>
+  </si>
+  <si>
+    <t>power_net_delay_ns_4</t>
+  </si>
+  <si>
+    <t>power_net_delay_ns_5</t>
+  </si>
+  <si>
+    <t>power_net_delay_ns_6</t>
+  </si>
+  <si>
+    <t>power_net_delay_ns_7</t>
+  </si>
+  <si>
+    <t>gate_period_us</t>
+  </si>
+  <si>
+    <t>cds1_rise_us</t>
+  </si>
+  <si>
+    <t>cds1_fall_us</t>
+  </si>
+  <si>
+    <t>cds2_rise_us</t>
+  </si>
+  <si>
+    <t>cds2_fall_us</t>
+  </si>
+  <si>
+    <t>clock_div_ratio</t>
+  </si>
+  <si>
+    <t>clock_frequency_MHz</t>
+  </si>
+  <si>
+    <t>power_net_duty_percent_0_min</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>power_net_duty_percent_1_min</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>power_net_duty_percent_2_min</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>power_net_duty_percent_3_min</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>power_net_duty_percent_4_min</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>power_net_duty_percent_5_min</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>power_net_duty_percent_6_min</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>power_net_duty_percent_7_min</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>power_net_duty_percent_0_max</t>
+  </si>
+  <si>
+    <t>power_net_duty_percent_1_max</t>
+  </si>
+  <si>
+    <t>power_net_duty_percent_2_max</t>
+  </si>
+  <si>
+    <t>power_net_duty_percent_3_max</t>
+  </si>
+  <si>
+    <t>power_net_duty_percent_4_max</t>
+  </si>
+  <si>
+    <t>power_net_duty_percent_5_max</t>
+  </si>
+  <si>
+    <t>power_net_duty_percent_6_max</t>
+  </si>
+  <si>
+    <t>power_net_duty_percent_7_max</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAF7"/>
+        <fgColor rgb="FFD9EAF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -55,87 +234,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -423,335 +543,306 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B35"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B43"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>parameter</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>pl_dcdc_clk_name</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr" s="2">
-        <is>
-          <t>PL_DCDC_CLK3</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>pl_dcdc_clk_delay_clks</t>
-        </is>
-      </c>
-      <c r="B3" t="n" s="2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>pl_dcdc_clk_delay_ns</t>
-        </is>
+      <c r="B3" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>5</v>
       </c>
       <c r="B4" s="2">
         <f>ROUND((1/175)*B3*10^3,1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>power_net_name_0</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr" s="2">
-        <is>
-          <t>4.3V_CHG</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>power_net_name_1</t>
-        </is>
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>8</v>
       </c>
       <c r="B6" s="2"/>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>power_net_name_2</t>
-        </is>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>9</v>
       </c>
       <c r="B7" s="2"/>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>power_net_name_3</t>
-        </is>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>10</v>
       </c>
       <c r="B8" s="2"/>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>power_net_name_4</t>
-        </is>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>11</v>
       </c>
       <c r="B9" s="2"/>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>power_net_name_5</t>
-        </is>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>12</v>
       </c>
       <c r="B10" s="2"/>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>power_net_name_6</t>
-        </is>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>13</v>
       </c>
       <c r="B11" s="2"/>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>power_net_name_7</t>
-        </is>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>14</v>
       </c>
       <c r="B12" s="2"/>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>power_net_delay_ns_0</t>
-        </is>
-      </c>
-      <c r="B13" t="n" s="2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="2">
         <v>42</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>power_net_delay_ns_1</t>
-        </is>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>16</v>
       </c>
       <c r="B14" s="2"/>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>power_net_delay_ns_2</t>
-        </is>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>17</v>
       </c>
       <c r="B15" s="2"/>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>power_net_delay_ns_3</t>
-        </is>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>18</v>
       </c>
       <c r="B16" s="2"/>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>power_net_delay_ns_4</t>
-        </is>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>19</v>
       </c>
       <c r="B17" s="2"/>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>power_net_delay_ns_5</t>
-        </is>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>20</v>
       </c>
       <c r="B18" s="2"/>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>power_net_delay_ns_6</t>
-        </is>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>21</v>
       </c>
       <c r="B19" s="2"/>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>power_net_delay_ns_7</t>
-        </is>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>22</v>
       </c>
       <c r="B20" s="2"/>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>power_net_duty_percent_0</t>
-        </is>
-      </c>
-      <c r="B21" t="n" s="2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="2">
+        <v>18.25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="2"/>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="2"/>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" s="2"/>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" s="2"/>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" s="2"/>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27" s="2"/>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="2"/>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="2">
         <v>36.5</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>power_net_duty_percent_1</t>
-        </is>
-      </c>
-      <c r="B22" s="2"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>power_net_duty_percent_2</t>
-        </is>
-      </c>
-      <c r="B23" s="2"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>power_net_duty_percent_3</t>
-        </is>
-      </c>
-      <c r="B24" s="2"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>power_net_duty_percent_4</t>
-        </is>
-      </c>
-      <c r="B25" s="2"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>power_net_duty_percent_5</t>
-        </is>
-      </c>
-      <c r="B26" s="2"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>power_net_duty_percent_6</t>
-        </is>
-      </c>
-      <c r="B27" s="2"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>power_net_duty_percent_7</t>
-        </is>
-      </c>
-      <c r="B28" s="2"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>gate_period_us</t>
-        </is>
-      </c>
-      <c r="B29" t="n" s="2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="2"/>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="2"/>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="2"/>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="2"/>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="2"/>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>44</v>
+      </c>
+      <c r="B35" s="2"/>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36" s="2"/>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>23</v>
+      </c>
+      <c r="B37" s="2">
         <v>48</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>cds1_rise_us</t>
-        </is>
-      </c>
-      <c r="B30" t="n" s="2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>24</v>
+      </c>
+      <c r="B38" s="2">
         <v>0.64</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>cds1_fall_us</t>
-        </is>
-      </c>
-      <c r="B31" t="n" s="2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>25</v>
+      </c>
+      <c r="B39" s="2">
         <v>18.2</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>cds2_rise_us</t>
-        </is>
-      </c>
-      <c r="B32" t="n" s="2">
-        <v>32.8</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>cds2_fall_us</t>
-        </is>
-      </c>
-      <c r="B33" t="n" s="2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>26</v>
+      </c>
+      <c r="B40" s="2">
+        <v>32.799999999999997</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>27</v>
+      </c>
+      <c r="B41" s="2">
         <v>47.2</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>clock_div_ratio</t>
-        </is>
-      </c>
-      <c r="B34" t="n" s="2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>28</v>
+      </c>
+      <c r="B42" s="2">
         <v>84</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>clock_frequency_MHz</t>
-        </is>
-      </c>
-      <c r="B35" s="2">
-        <f>ROUND(175/B34,2)</f>
-        <v/>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>29</v>
+      </c>
+      <c r="B43" s="2">
+        <f>ROUND(175/B42,2)</f>
+        <v>2.08</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/設定ファイル/シリアル_48us/シリアル_48us_CLK3.xlsx
+++ b/設定ファイル/シリアル_48us/シリアル_48us_CLK3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e12206\GitHub\DCDC_clock_simulator\設定ファイル\シリアル_48us\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53D95349-7C1C-42F3-9EF2-90739BECF3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEAF084C-4326-47B7-B813-F8E5A50A76ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4150" yWindow="0" windowWidth="14550" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="config" sheetId="1" r:id="rId1"/>
@@ -689,7 +689,7 @@
         <v>30</v>
       </c>
       <c r="B21" s="2">
-        <v>18.25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
@@ -739,7 +739,7 @@
         <v>38</v>
       </c>
       <c r="B29" s="2">
-        <v>36.5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
